--- a/光伏配储项目/电价数据/2026/方红站.xlsx
+++ b/光伏配储项目/电价数据/2026/方红站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.48281</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7547999999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.54084</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5562</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.48392</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.47425</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.43907</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.40904</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.40889</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38236</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.40663</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40381</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.42959</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47214</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.1532</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.23221</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.00843</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.21604</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.02236</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.07657</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.03644</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.15734</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.16102</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.14673</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28974</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.09816</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.01764</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.51098</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5372400000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73391</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.12296</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39478</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.19605</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66125</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.86549</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47411</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.1964</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.40907</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.27344</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.98458</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.28194</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.47365</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43671</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6830900000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.73326</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.08095</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95366</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.89318</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.80048</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7613099999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51449</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48351</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46455</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41768</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42757</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7171900000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8896799999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.94272</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5027200000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5250199999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50951</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5096499999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49163</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47311</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.42891</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.39329</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4468</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.15514</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.01492</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.07664</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.49206</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48862</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5042</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.13484</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.14596</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.25924</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.00027</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.05005</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.5644600000000001</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.04017</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.02175</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.6718200000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.6023999999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.08683</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.7942100000000001</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.26633</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.16657</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.25645</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.25542</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.26855</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.57212</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.59215</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.74249</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.16099</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.24667</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.12977</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.83693</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20486</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10585</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25625</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02206</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.09006</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.65118</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98295</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9140199999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.95699</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7780499999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.88793</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.73714</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.78016</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45111</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.72809</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.76127</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45109</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4452</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33493</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5131599999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49325</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48968</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44455</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43162</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44769</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47781</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44644</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4416600000000001</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39657</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.21402</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.05881</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.43048</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.22099</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7795800000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.47906</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.42273</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42952</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.42956</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.43325</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.42939</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.51422</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.4861</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28467</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62101</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6461399999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46616</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50598</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.46838</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.54843</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.48594</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.61312</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42407</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.4839</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6175499999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.57136</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.55741</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.71717</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.60209</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5188200000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.41735</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.55318</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43366</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34234</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51446</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5032099999999999</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43871</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39298</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45236</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39666</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42033</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43132</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40376</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.09972</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.06338000000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.15247</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.05584</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.55955</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.24415</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.17244</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.15548</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.11149</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.62417</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.44451</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40692</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28148</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.40917</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.4747</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.4497</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50954</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46702</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47492</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.48648</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.54915</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55775</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.49471</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46906</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50486</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42661</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42235</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32118</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.1103</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.26826</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.07745999999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.26645</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.15747</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.09654</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13136</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.10536</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.008070000000000001</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.16772</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.16702</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.04815</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.00451</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.00518</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.01817</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.23986</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29549</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.42091</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.42156</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.41948</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.43272</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.42447</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43795</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.48672</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.41506</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.42429</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.5471900000000001</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.37194</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.8610399999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.46213</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.57372</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5327200000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.54623</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.4030899999999999</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.42048</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.43314</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.42201</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.6140399999999999</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.41447</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.43023</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10215</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04319</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0449</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00487</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19638</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04437</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.15065</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.02763</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05053</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.34763</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3236</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.43199</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42904</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45783</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39238</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40239</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78547</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91418</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18704</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86921</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.57756</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03288</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79095</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.54286</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729400000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20695</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.43161</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.45574</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4572</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45511</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.37434</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.42271</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.44865</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.66926</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.50436</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.62849</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.81665</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8842899999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47125</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.49802</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.6683600000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.49963</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.05017</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.80529</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.87448</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.51659</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.9069400000000001</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.83866</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59004</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.47709</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.4812</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5417000000000001</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.48485</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.44523</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.37208</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.93637</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.39329</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.5296900000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.47608</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.45765</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.55332</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.42413</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.47026</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.46789</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.61533</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.41635</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.22171</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.09048</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.26401</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.28942</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26803</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20081</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.44733</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25863</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.38349</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27972</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.43224</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.53525</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42786</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.4745</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4776</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.46365</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4654</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.7858999999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.43373</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.9484199999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.48246</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.20308</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7304299999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.82237</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6816</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.80643</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.59893</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.47658</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.52762</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.46524</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.49857</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.44047</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43603</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.47931</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.6159199999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43565</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45796</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.48544</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45744</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.41008</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.51516</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.55104</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.41865</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.44523</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.5231399999999999</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.4356</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.43193</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.46942</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.5126799999999999</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.47559</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.51766</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.46083</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.63152</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.56259</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25173</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15692</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27567</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01817</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26443</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25904</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.44825</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.38174</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36435</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.41467</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.65384</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.5498</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.02415</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.55633</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.52298</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.41872</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.51174</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.43151</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.40623</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.37056</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.5200900000000001</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.40499</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.41612</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.41794</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.41057</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.43178</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.42895</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.42866</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.5451</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.51747</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.5556599999999999</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.44488</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.53124</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.49764</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.44699</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.41326</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.21456</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.07255</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.09973</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.1168</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.08451</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.09196</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26512</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.10311</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.23046</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.08769</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25635</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.12797</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05379</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.06548000000000001</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.05751</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16207</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.07614</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28951</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.37641</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.39899</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.42889</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.42695</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.45621</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.40255</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.44061</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.54587</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.46495</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.44785</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.46798</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.45817</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.54501</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.5312</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.52715</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.53374</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.46247</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.42267</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.41692</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.41066</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.40606</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.40549</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.39097</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.68121</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.40731</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.56811</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.49586</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.48419</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.4152</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.43143</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.42828</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.44727</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.42549</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.39486</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.44406</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.43238</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.38443</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.54423</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.39817</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.26502</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26692</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2355</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.17298</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.22069</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21489</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.19468</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.23981</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.26871</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25718</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.43593</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.4054700000000001</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.40525</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.40879</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.52237</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.42005</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38417</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.36401</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.43859</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.42544</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.43229</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3949</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.6340399999999999</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.64155</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.42199</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.39258</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.37259</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.43679</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.41983</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.41346</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.40166</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.45453</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.13309</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43506</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.67788</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5171399999999999</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.4696</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46266</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.43733</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2594</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.26167</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.17258</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.18465</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.27534</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.2545</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.54936</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.43435</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.12988</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43347</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.39655</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.39023</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.57931</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.48087</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46626</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44773</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71968</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.39032</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.05581</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.89925</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.72629</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5285299999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26959</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40932</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.6688999999999999</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.42508</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.51732</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.42577</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.43541</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.4070299999999999</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.41979</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.44409</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.46658</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.44653</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.43689</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.37336</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.43275</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.30273</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.4076</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.40816</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.38186</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.47644</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.41865</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.43099</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.38107</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.42625</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.46069</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.44674</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.50741</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.4443</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.45832</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.46818</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.42193</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.36858</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.59741</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.42366</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.38168</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.42997</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42166</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.42251</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.49152</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43492</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6748999999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.07939</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.52383</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.54683</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.37427</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.43047</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.40197</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.38946</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.39137</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.39031</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.42684</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.42447</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26104</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.10922</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.23421</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.20138</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.12714</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.22021</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.25136</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.25319</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.25247</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.15521</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.21769</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.25888</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.24907</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29094</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39639</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.42853</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.47195</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.56602</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.50826</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.47019</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.68086</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6384099999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.65687</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.64827</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8487899999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.6215700000000001</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.19755</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.67172</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.52452</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43623</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42345</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.46251</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.6059600000000001</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.50398</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.48547</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.38978</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.59154</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.7278</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.63251</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.90639</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.47857</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.48037</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.45575</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.47017</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.46356</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.47844</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.44858</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.41363</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.45949</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.45689</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.43686</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.48854</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.43834</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.48558</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.4423</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.47234</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.46204</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.47808</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.46711</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.5589</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.54692</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.73115</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.62412</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.54031</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.61311</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.53638</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46383</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.46545</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46615</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5461900000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45354</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.4705299999999999</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.44874</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.4318</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39657</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.64712</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.64281</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.22575</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38189</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.41349</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.40921</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.41666</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.43046</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.43852</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.47214</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.50851</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.59845</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.5373</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.63758</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.63988</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.7059099999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.9503200000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.17719</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.29481</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.9347000000000001</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.10323</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.91887</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.69636</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.14621</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78839</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.64195</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.69126</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.56101</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.59088</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.5884199999999999</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.57664</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.56835</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.47818</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.69574</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.49627</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.51915</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5439700000000001</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45335</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.5288999999999999</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43502</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.45425</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.57612</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.46845</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.47743</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.45139</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.43599</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.41891</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.61897</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.43227</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.40897</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.45702</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.45884</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.41418</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40912</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40468</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.44195</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.40566</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.25908</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40504</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.01653</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.43962</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.51598</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01759</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.10589</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.02929</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.38655</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.41502</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.43131</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.49071</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.46983</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.45442</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5231</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42696</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.46704</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.49294</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.5039</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.5197200000000001</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.49773</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.40177</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.46542</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.47555</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.43396</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.47174</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.50997</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.48417</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.52774</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.50836</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.46614</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.42087</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.62487</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.4769</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.49281</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.49852</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.45959</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.48179</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.46801</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.62373</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41806</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.5930599999999999</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.5871499999999999</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.46762</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.60088</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.4670299999999999</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.56225</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.44333</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.45463</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.43273</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.44851</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.45498</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.46146</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.5470499999999999</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.46793</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.54526</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.56143</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.49387</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.40507</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.42376</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.56121</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.18119</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.20921</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.21135</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.22953</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.07074</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.10877</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.18282</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22322</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27345</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21425</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27657</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.44707</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.46018</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.4022</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.45352</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.41119</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.45128</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.41682</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.47428</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.4978399999999999</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.47151</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.42475</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.44372</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.44005</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.43447</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.48919</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.50425</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.46343</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.46409</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.42547</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.5159600000000001</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.40358</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.50845</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.48137</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.51944</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.51068</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.5106700000000001</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.50444</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.50444</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.50818</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.51185</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.50444</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.50505</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.51974</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.5192899999999999</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.52301</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.03362</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02288</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.0149</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0431</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04105</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02949</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.0369</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00151</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27936</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03617</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01497</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03557</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20576</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2691</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28045</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.51575</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.39129</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.54049</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.42942</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.41038</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.18887</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.02045</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.49414</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.87746</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5267000000000001</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.54134</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.59601</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.45163</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.5099900000000001</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.48457</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.47899</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.6380399999999999</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.46557</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.43945</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.66053</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.5710499999999999</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.6518699999999999</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.59651</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.6535700000000001</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.62137</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.60409</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.62903</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.67083</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46583</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.53918</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.5946399999999999</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52246</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.50795</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.40982</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.91147</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87393</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.00048</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.009210000000000001</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04835</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04293</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.04689</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.00437</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25439</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.42813</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.44874</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.41186</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.39797</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.45027</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.04629</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.15578</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.11429</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.00052</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.14176</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.04833</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.14931</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8630800000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.86134</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8654700000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.96229</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.14419</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.14529</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.13846</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.39734</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.42259</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.42243</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.60538</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.8942599999999999</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.47186</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.83988</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.51907</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.62439</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.51995</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.5202899999999999</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40624</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.48721</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.5315800000000001</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.41138</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.42574</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.6660900000000001</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.44736</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.47288</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.43744</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.45996</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.46517</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.62149</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.53739</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.50795</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.50605</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.61656</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.67315</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.49707</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.52428</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.3909</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.40364</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.07717</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.27007</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.2562</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.24302</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26083</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36435</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41752</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.42983</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.42009</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.41433</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.45127</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.6303799999999999</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.24639</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.50775</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.91528</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.6136900000000001</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.5482</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.53899</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.48931</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.6766799999999999</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.40881</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.42674</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.40164</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.41301</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.40362</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.49824</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.51512</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.48512</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.47913</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.45548</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.44952</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.44345</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.40536</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.40822</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40846</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.38349</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.40733</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.39709</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5489400000000001</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.43744</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.41884</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.8590599999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.01407</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.8394299999999999</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.7795700000000001</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.60042</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.38834</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41559</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42603</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41046</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.99971</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8317100000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46147</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.46682</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.57986</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.55688</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.65197</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.81637</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.57189</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.92457</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.8091499999999999</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.61229</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.6149600000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43804</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.4657</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.54064</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.41531</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.5402100000000001</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.44945</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.44894</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.40768</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.39498</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.40279</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.52984</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.44268</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.45126</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.43832</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.42717</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.40748</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.38843</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.40498</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.41382</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.46121</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.42298</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43405</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38979</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.28776</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.40088</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.41087</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40843</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43342</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.44542</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.45467</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.52515</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.66152</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.7138</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.78301</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.54634</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.43903</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.7785299999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4854</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.62612</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.9464</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.5638200000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.5438500000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5550900000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.01674</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.48095</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.49542</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.43888</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40765</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.40732</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.40366</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.45842</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.6143200000000001</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.42505</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.42026</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.44583</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3905</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17549</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.27076</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28951</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.17347</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20403</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.09619</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.18606</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01566</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.05352000000000001</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26462</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.00647</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02823</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03803</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.10862</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.02504</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>-0.00029</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.23162</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.18184</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.20716</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.43694</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.37312</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.4039700000000001</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42078</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.54386</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43981</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.45783</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.5199199999999999</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47407</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.42594</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42351</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.42558</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.44678</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.48051</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40854</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.40382</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.41945</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.26103</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.43527</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.24568</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.46962</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.43503</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.40627</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.42574</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.41632</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.41091</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.40636</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.40499</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.40108</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.38975</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.41151</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39517</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.39633</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.23079</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.26683</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28379</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.11022</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.13893</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27149</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.41607</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42173</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42502</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.43252</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.43451</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.44111</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.40738</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39827</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.42151</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42406</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41061</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38907</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.48328</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.45449</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.40379</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40555</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39728</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.38828</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17693</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29045</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14656</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19983</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.02346</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2418</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.0343</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.02674</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.02053</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.02461</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13171</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.01811</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.06336</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17474</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.01303</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26733</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15459</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25805</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.02241</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.22132</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.03992</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14791</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26415</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25874</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.4221</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.41802</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.40832</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.43032</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.43168</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41692</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41654</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.4085</v>
       </c>
     </row>
   </sheetData>
